--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 17,94</t>
+          <t>-2,79; 18,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 16,3</t>
+          <t>-6,09; 15,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,31; 57,76</t>
+          <t>38,97; 57,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 13,4</t>
+          <t>-7,69; 12,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 6,43</t>
+          <t>-13,3; 7,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 46,43</t>
+          <t>17,59; 46,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 12,48</t>
+          <t>-2,92; 11,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,44</t>
+          <t>-6,3; 8,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 49,02</t>
+          <t>30,21; 48,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 78,29</t>
+          <t>-9,24; 80,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 71,4</t>
+          <t>-18,34; 64,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116,8; 267,64</t>
+          <t>111,35; 260,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 46,71</t>
+          <t>-20,8; 42,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 22,9</t>
+          <t>-35,38; 25,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,38; 160,28</t>
+          <t>49,52; 158,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 45,04</t>
+          <t>-8,13; 43,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 30,91</t>
+          <t>-18,68; 29,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,49; 182,02</t>
+          <t>89,32; 178,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 15,3</t>
+          <t>-3,48; 16,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 12,11</t>
+          <t>-5,35; 12,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,47; 51,41</t>
+          <t>31,71; 50,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 11,63</t>
+          <t>-6,49; 10,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 6,57</t>
+          <t>-10,1; 7,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,31; 45,51</t>
+          <t>28,8; 45,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,45</t>
+          <t>-2,8; 9,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 6,54</t>
+          <t>-5,14; 6,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,5; 46,32</t>
+          <t>32,91; 45,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 58,13</t>
+          <t>-9,98; 61,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 46,45</t>
+          <t>-15,4; 47,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,92; 206,37</t>
+          <t>89,07; 193,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 37,54</t>
+          <t>-15,9; 34,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 20,26</t>
+          <t>-23,83; 23,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,69; 144,62</t>
+          <t>68,82; 148,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 30,82</t>
+          <t>-7,64; 31,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 21,57</t>
+          <t>-13,91; 21,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,46; 153,39</t>
+          <t>87,68; 153,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 4,56</t>
+          <t>-16,09; 4,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 0,67</t>
+          <t>-19,74; 0,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,77; 51,6</t>
+          <t>32,74; 52,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 2,93</t>
+          <t>-18,04; 1,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 1,43</t>
+          <t>-18,38; 0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,85; 44,36</t>
+          <t>26,45; 44,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,35</t>
+          <t>-14,76; -0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -2,21</t>
+          <t>-16,21; -2,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 45,5</t>
+          <t>31,46; 45,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 11,91</t>
+          <t>-38,75; 14,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 2,15</t>
+          <t>-43,62; 0,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,41; 158,25</t>
+          <t>70,77; 154,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 8,53</t>
+          <t>-38,73; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 4,14</t>
+          <t>-38,97; 2,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,58; 123,18</t>
+          <t>55,19; 125,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -1,12</t>
+          <t>-33,86; -1,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,88; -6,04</t>
+          <t>-36,45; -6,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,29; 123,91</t>
+          <t>68,49; 123,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 12,22</t>
+          <t>-5,92; 12,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 13,57</t>
+          <t>-3,77; 13,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,47; 55,32</t>
+          <t>38,22; 55,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 4,43</t>
+          <t>-14,76; 3,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 4,87</t>
+          <t>-13,71; 3,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,62; 52,24</t>
+          <t>36,22; 52,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 4,47</t>
+          <t>-7,92; 4,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 5,99</t>
+          <t>-5,96; 6,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,15; 50,72</t>
+          <t>39,62; 51,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 42,62</t>
+          <t>-15,9; 43,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 48,15</t>
+          <t>-9,83; 47,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98,13; 199,99</t>
+          <t>96,35; 193,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 12,52</t>
+          <t>-35,87; 11,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 15,17</t>
+          <t>-32,87; 10,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,67; 166,69</t>
+          <t>86,02; 167,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 14,45</t>
+          <t>-21,04; 15,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 18,62</t>
+          <t>-15,46; 22,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102,7; 160,29</t>
+          <t>99,9; 164,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,52</t>
+          <t>-2,38; 7,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,68</t>
+          <t>-3,69; 5,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,83; 49,82</t>
+          <t>40,01; 50,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,18</t>
+          <t>-7,06; 2,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,42</t>
+          <t>-9,02; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,66</t>
+          <t>33,1; 42,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,49</t>
+          <t>-3,6; 3,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,03</t>
+          <t>-5,18; 1,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,31; 44,87</t>
+          <t>37,91; 44,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 24,59</t>
+          <t>-7,02; 24,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 18,32</t>
+          <t>-10,68; 19,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110,54; 165,8</t>
+          <t>110,29; 166,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 9,37</t>
+          <t>-17,82; 6,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 1,23</t>
+          <t>-22,12; 1,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,5; 122,86</t>
+          <t>83,62; 123,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,57</t>
+          <t>-9,66; 10,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 6,1</t>
+          <t>-14,18; 4,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103,81; 134,42</t>
+          <t>101,06; 134,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 18,96</t>
+          <t>-3,32; 19,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 15,09</t>
+          <t>-5,47; 17,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,97; 57,39</t>
+          <t>39,08; 57,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 12,21</t>
+          <t>-9,35; 12,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 7,34</t>
+          <t>-13,19; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 46,14</t>
+          <t>16,2; 46,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 11,79</t>
+          <t>-2,73; 11,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 8,51</t>
+          <t>-6,87; 8,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,21; 48,32</t>
+          <t>29,96; 49,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 80,65</t>
+          <t>-10,73; 80,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 64,14</t>
+          <t>-16,61; 76,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111,35; 260,32</t>
+          <t>113,0; 261,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 42,03</t>
+          <t>-24,01; 42,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 25,31</t>
+          <t>-35,53; 24,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,52; 158,49</t>
+          <t>46,79; 162,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 43,36</t>
+          <t>-8,07; 43,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 29,43</t>
+          <t>-20,37; 29,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,32; 178,44</t>
+          <t>89,69; 180,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 16,08</t>
+          <t>-3,23; 15,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 12,45</t>
+          <t>-5,81; 12,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,71; 50,38</t>
+          <t>33,2; 51,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 10,84</t>
+          <t>-6,82; 11,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 7,72</t>
+          <t>-10,36; 7,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,8; 45,88</t>
+          <t>28,76; 46,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,79</t>
+          <t>-2,18; 11,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,55</t>
+          <t>-5,21; 6,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,91; 45,97</t>
+          <t>34,17; 46,54</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 61,87</t>
+          <t>-9,6; 64,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 47,13</t>
+          <t>-16,26; 46,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,07; 193,49</t>
+          <t>93,92; 204,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 34,49</t>
+          <t>-15,86; 35,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 23,54</t>
+          <t>-25,2; 23,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,82; 148,84</t>
+          <t>67,32; 145,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 31,25</t>
+          <t>-5,65; 36,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 21,54</t>
+          <t>-14,22; 22,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,68; 153,88</t>
+          <t>91,93; 154,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 4,96</t>
+          <t>-16,68; 4,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 0,02</t>
+          <t>-18,19; 0,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,74; 52,08</t>
+          <t>31,71; 52,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 1,98</t>
+          <t>-19,99; 1,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 0,79</t>
+          <t>-17,34; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 44,35</t>
+          <t>25,89; 44,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,76; -0,47</t>
+          <t>-14,94; -0,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,21; -2,24</t>
+          <t>-16,02; -1,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,46; 45,6</t>
+          <t>31,62; 45,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 14,31</t>
+          <t>-37,65; 14,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 0,13</t>
+          <t>-42,5; 1,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,77; 154,83</t>
+          <t>67,62; 157,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 5,54</t>
+          <t>-39,89; 6,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 2,16</t>
+          <t>-37,74; 5,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55,19; 125,89</t>
+          <t>53,5; 123,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -1,3</t>
+          <t>-33,57; -0,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,45; -6,12</t>
+          <t>-35,52; -4,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,49; 123,67</t>
+          <t>68,41; 125,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 12,16</t>
+          <t>-6,57; 12,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 13,55</t>
+          <t>-4,35; 13,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,22; 55,03</t>
+          <t>37,81; 54,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 3,56</t>
+          <t>-14,13; 3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 3,49</t>
+          <t>-13,1; 5,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,22; 52,54</t>
+          <t>36,07; 51,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 4,91</t>
+          <t>-7,36; 5,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 6,77</t>
+          <t>-6,37; 6,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,62; 51,12</t>
+          <t>39,66; 51,11</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 43,29</t>
+          <t>-17,87; 42,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 47,31</t>
+          <t>-11,39; 48,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96,35; 193,22</t>
+          <t>97,04; 194,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 11,57</t>
+          <t>-34,19; 10,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 10,63</t>
+          <t>-32,59; 15,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,02; 167,73</t>
+          <t>86,18; 163,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 15,24</t>
+          <t>-19,51; 15,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 22,18</t>
+          <t>-16,51; 19,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>99,9; 164,24</t>
+          <t>102,84; 163,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,34</t>
+          <t>-1,92; 7,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,89</t>
+          <t>-3,58; 6,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,01; 50,01</t>
+          <t>39,69; 49,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,23</t>
+          <t>-6,68; 2,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 0,32</t>
+          <t>-8,87; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,76</t>
+          <t>33,02; 42,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,72</t>
+          <t>-3,03; 3,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,55</t>
+          <t>-4,56; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,76</t>
+          <t>37,94; 44,93</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 24,17</t>
+          <t>-5,61; 25,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 19,58</t>
+          <t>-10,0; 19,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110,29; 166,04</t>
+          <t>109,53; 163,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 6,14</t>
+          <t>-17,07; 8,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 1,17</t>
+          <t>-22,54; 1,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,62; 123,77</t>
+          <t>83,66; 124,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 10,98</t>
+          <t>-8,28; 10,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 4,52</t>
+          <t>-12,24; 5,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>101,06; 134,81</t>
+          <t>102,94; 136,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,85</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,08</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,39</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>49,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40,78</t>
+          <t>43,55</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 19,09</t>
+          <t>-7,41; 13,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 17,04</t>
+          <t>-13,52; 6,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,08; 57,66</t>
+          <t>20,33; 48,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 12,34</t>
+          <t>-2,66; 17,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 6,85</t>
+          <t>-5,53; 16,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 46,64</t>
+          <t>39,53; 58,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 11,85</t>
+          <t>-2,41; 12,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 8,22</t>
+          <t>-6,56; 8,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,96; 49,02</t>
+          <t>33,94; 50,43</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-10,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>28,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>18,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>176,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>178,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131,86%</t>
+          <t>140,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 80,8</t>
+          <t>-19,24; 46,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 76,83</t>
+          <t>-35,1; 22,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113,0; 261,36</t>
+          <t>57,46; 169,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 42,62</t>
+          <t>-8,12; 78,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 24,37</t>
+          <t>-17,58; 71,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,79; 162,34</t>
+          <t>119,06; 270,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 43,32</t>
+          <t>-6,74; 45,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 29,94</t>
+          <t>-19,7; 30,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,69; 180,51</t>
+          <t>100,68; 191,09</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,98</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,91</t>
+          <t>45,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40,26</t>
+          <t>41,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 15,87</t>
+          <t>-6,39; 11,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 12,13</t>
+          <t>-10,31; 6,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 51,86</t>
+          <t>29,39; 46,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 11,48</t>
+          <t>-2,79; 15,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 7,26</t>
+          <t>-4,71; 12,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,76; 46,1</t>
+          <t>36,39; 53,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,09</t>
+          <t>-3,26; 9,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 6,91</t>
+          <t>-5,7; 6,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,17; 46,54</t>
+          <t>35,48; 47,61</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-3,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>105,93%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139,16%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-3,98%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>103,02%</t>
+          <t>147,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>118,56%</t>
+          <t>123,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 64,83</t>
+          <t>-15,31; 37,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 46,9</t>
+          <t>-24,66; 20,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,92; 204,61</t>
+          <t>70,05; 148,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 35,59</t>
+          <t>-9,35; 58,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 23,32</t>
+          <t>-13,69; 46,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,32; 145,51</t>
+          <t>100,56; 213,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 36,38</t>
+          <t>-8,88; 30,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 22,94</t>
+          <t>-15,29; 21,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,93; 154,06</t>
+          <t>94,07; 159,22</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,99</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,33</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35,28</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-6,57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41,76</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,26</t>
+          <t>37,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38,5</t>
+          <t>36,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 4,91</t>
+          <t>-17,54; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 0,6</t>
+          <t>-18,09; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,71; 52,31</t>
+          <t>25,58; 44,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 1,83</t>
+          <t>-16,57; 4,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 2,11</t>
+          <t>-19,08; 0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 44,97</t>
+          <t>28,15; 46,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -0,15</t>
+          <t>-13,71; -0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -1,89</t>
+          <t>-15,68; -2,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,62; 45,97</t>
+          <t>29,31; 42,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,92%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-16,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-24,45%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106,56%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-18,92%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,72%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 14,23</t>
+          <t>-37,57; 8,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 1,79</t>
+          <t>-38,87; 4,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,62; 157,04</t>
+          <t>54,08; 123,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 6,41</t>
+          <t>-38,64; 11,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 5,61</t>
+          <t>-44,08; 2,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,5; 123,39</t>
+          <t>62,96; 142,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,57; -0,23</t>
+          <t>-31,32; -1,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,52; -4,76</t>
+          <t>-35,88; -6,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,41; 125,49</t>
+          <t>64,59; 116,41</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44,93</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,33</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,51</t>
+          <t>46,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45,49</t>
+          <t>45,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 12,24</t>
+          <t>-15,14; 4,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 13,7</t>
+          <t>-11,99; 4,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,81; 54,13</t>
+          <t>36,86; 52,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 3,46</t>
+          <t>-6,53; 12,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 5,01</t>
+          <t>-4,64; 13,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,07; 51,29</t>
+          <t>38,58; 55,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 5,22</t>
+          <t>-8,53; 4,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 6,33</t>
+          <t>-6,27; 5,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,66; 51,11</t>
+          <t>40,21; 50,91</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-15,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-11,71%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121,6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>13,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>137,51%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-15,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-11,71%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>120,47%</t>
+          <t>137,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128,95%</t>
+          <t>129,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 42,54</t>
+          <t>-36,56; 12,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 48,01</t>
+          <t>-30,01; 15,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,04; 194,81</t>
+          <t>88,94; 168,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 10,8</t>
+          <t>-17,1; 42,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 15,67</t>
+          <t>-12,15; 48,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,18; 163,87</t>
+          <t>97,43; 197,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 15,98</t>
+          <t>-21,67; 14,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 19,29</t>
+          <t>-16,26; 18,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102,84; 163,65</t>
+          <t>102,94; 160,55</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>39,6</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>44,97</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,98</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>44,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41,52</t>
+          <t>42,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,84</t>
+          <t>-6,71; 3,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,17</t>
+          <t>-8,87; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,69; 49,51</t>
+          <t>34,21; 43,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,96</t>
+          <t>-2,33; 7,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,61</t>
+          <t>-3,79; 5,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,02; 42,94</t>
+          <t>39,69; 49,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,71</t>
+          <t>-3,2; 3,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,92</t>
+          <t>-4,87; 2,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,94; 44,93</t>
+          <t>39,0; 45,16</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,83%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-10,66%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>106,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>136,65%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,83%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-10,66%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>102,76%</t>
+          <t>135,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118,09%</t>
+          <t>119,51%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 25,77</t>
+          <t>-16,67; 9,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 19,76</t>
+          <t>-22,15; 1,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109,53; 163,0</t>
+          <t>84,68; 126,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 8,48</t>
+          <t>-6,75; 24,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 1,39</t>
+          <t>-10,76; 18,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,66; 124,13</t>
+          <t>110,17; 164,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 10,99</t>
+          <t>-8,62; 10,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,8</t>
+          <t>-13,37; 6,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102,94; 136,72</t>
+          <t>104,99; 135,28</t>
         </is>
       </c>
     </row>
